--- a/backend/data/Book1.xlsx
+++ b/backend/data/Book1.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>LNDID</t>
   </si>
@@ -54,20 +54,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri Light"/>
-      <family val="1"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -78,7 +71,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -86,31 +79,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -392,7 +367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32.21875" customWidth="1"/>
@@ -421,242 +396,22 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>2023</v>
-      </c>
-      <c r="E2" s="3">
-        <v>50</v>
+        <v>2026</v>
+      </c>
+      <c r="E2" s="2">
+        <v>80</v>
       </c>
       <c r="F2" s="1">
-        <v>44986.432303240741</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <v>2024</v>
-      </c>
-      <c r="E3" s="3">
-        <v>60</v>
-      </c>
-      <c r="F3" s="1">
-        <v>45352.432303240741</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>2025</v>
-      </c>
-      <c r="E4" s="3">
-        <v>70</v>
-      </c>
-      <c r="F4" s="1">
-        <v>45717.432303240741</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5">
-        <v>2</v>
-      </c>
-      <c r="D5">
-        <v>2026</v>
-      </c>
-      <c r="E5" s="3">
-        <v>80</v>
-      </c>
-      <c r="F5" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-      <c r="D6">
-        <v>2026</v>
-      </c>
-      <c r="E6" s="3">
-        <v>81</v>
-      </c>
-      <c r="F6" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>2026</v>
-      </c>
-      <c r="E7" s="3">
-        <v>82</v>
-      </c>
-      <c r="F7" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8">
-        <v>5</v>
-      </c>
-      <c r="D8">
-        <v>2026</v>
-      </c>
-      <c r="E8" s="3">
-        <v>83</v>
-      </c>
-      <c r="F8" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9">
-        <v>6</v>
-      </c>
-      <c r="D9">
-        <v>2026</v>
-      </c>
-      <c r="E9" s="3">
-        <v>84</v>
-      </c>
-      <c r="F9" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10">
-        <v>7</v>
-      </c>
-      <c r="D10">
-        <v>2026</v>
-      </c>
-      <c r="E10" s="3">
-        <v>85</v>
-      </c>
-      <c r="F10" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>8</v>
-      </c>
-      <c r="D11">
-        <v>2026</v>
-      </c>
-      <c r="E11" s="3">
-        <v>86</v>
-      </c>
-      <c r="F11" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12">
-        <v>9</v>
-      </c>
-      <c r="D12">
-        <v>2026</v>
-      </c>
-      <c r="E12" s="3">
-        <v>87</v>
-      </c>
-      <c r="F12" s="1">
-        <v>46082.432303240741</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>6</v>
-      </c>
-      <c r="B13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13">
-        <v>10</v>
-      </c>
-      <c r="D13">
-        <v>2026</v>
-      </c>
-      <c r="E13" s="3">
-        <v>88</v>
-      </c>
-      <c r="F13" s="1">
         <v>46082.432303240741</v>
       </c>
     </row>
